--- a/光伏配储项目/电价数据/2026/挂绿站.xlsx
+++ b/光伏配储项目/电价数据/2026/挂绿站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS102"/>
+  <dimension ref="A1:CS129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -30511,6 +30510,7917 @@
       </c>
       <c r="CS102" t="n">
         <v>0.51413</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.75382</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.5781000000000001</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.59087</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.52478</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.51444</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.45493</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.45455</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0.10088</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>0.11244</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>0.10373</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0.12334</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0.09592000000000001</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>0.14883</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>0.19458</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0.09081</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0.11554</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>0.08896999999999999</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0.14798</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>0.21456</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>0.46006</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0.22591</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>0.20541</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>0.03329</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>0.58661</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>0.13366</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0.59749</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>0.50664</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>0.51946</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>1.37636</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>0.56969</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>0.56759</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>0.45624</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>0.6135700000000001</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>0.8091699999999999</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0.6495599999999999</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0.75844</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>1.02486</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0.66673</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>0.5876699999999999</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0.74552</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0.8035399999999999</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>0.6470499999999999</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0.61049</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0.52436</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>0.48097</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>0.47223</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>0.42607</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.69823</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.87527</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.9561499999999999</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.55603</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.51754</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.48679</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.61561</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0.87027</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>0.51085</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>0.49117</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0.75826</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>1.02044</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0.66351</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0.82329</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0.7583300000000001</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>0.66887</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0.73991</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0.9154800000000001</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>0.85141</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>0.49906</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>0.48916</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>0.52991</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>1.00218</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>0.66537</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>0.5870599999999999</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>0.5912500000000001</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>0.6072799999999999</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>0.79155</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>0.56986</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>0.6386000000000001</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>0.80386</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>0.5709299999999999</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>0.6768099999999999</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>0.8442200000000001</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0.72824</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0.68659</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0.6561399999999999</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0.7734099999999999</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0.5133300000000001</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1.30969</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0.76678</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>0.43913</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0.43258</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.5133799999999999</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.50829</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.5379400000000001</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.4777</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0.47368</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>0.21897</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>0.55449</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>1.05306</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0.6235599999999999</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>0.65859</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>0.50129</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0.50084</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>0.57037</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0.6472100000000001</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>0.65801</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>0.63687</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>0.47534</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>0.54643</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0.57259</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>0.91288</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>0.54199</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>0.62283</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>0.63325</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>0.5857599999999999</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0.47925</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0.43113</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0.46378</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0.44263</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>0.46586</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>0.42918</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>0.40332</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>0.34217</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.5269400000000001</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.49226</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.58013</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.45501</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>0.08237</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>0.21503</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>0.24227</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>0.53177</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>0.21226</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0.49803</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0.53564</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>0.51483</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>0.25066</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>0.14781</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>0.54377</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>0.85626</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>0.55002</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0.45558</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>0.32866</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.48513</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>0.04462</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>-0.03229</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>-0.04669</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>0.18309</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>0.22251</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>0.20524</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>-0.04922</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>-0.03915</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>0.21826</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>0.05635</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>-0.04932</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>0.0005200000000000001</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>0.05152</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>0.04352</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>0.10348</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>0.35019</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.65965</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>0.75405</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>0.11014</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>0.45461</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>0.00942</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>-0.04518</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>-0.04528</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>0.18304</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>0.18157</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>-0.04738000000000001</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>-0.04785</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>0.19984</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>0.14277</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>0.33502</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1.31701</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0.17237</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0.15861</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0.23611</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0.22652</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0.45692</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>0.15645</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>0.6220599999999999</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>0.92045</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>0.91459</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>0.86373</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>1.29685</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0.88855</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0.63183</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>1.18813</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0.8691</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>0.52965</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1.3319</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>1.03365</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0.5318099999999999</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0.79183</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>0.52743</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0.77383</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0.7782100000000001</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>0.87688</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>0.8743099999999999</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>0.49394</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1.40094</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1.20804</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.8789</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.55106</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.62288</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.53859</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.45597</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.45272</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0.41415</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0.5834</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>0.5947899999999999</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>0.59934</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>0.67571</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>0.4707</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>0.57913</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>0.86649</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>0.6190099999999999</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>0.8872599999999999</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>0.84123</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0.86233</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>0.71417</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>0.40778</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>0.35282</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.91565</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.46222</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.48969</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.45722</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0.49612</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>0.16815</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>0.19888</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>0.19112</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CM111" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="CN111" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CO111" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="CP111" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CQ111" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CR111" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="CS111" t="n">
+        <v>0.59026</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.8882599999999999</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.5824</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1.14679</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.6975800000000001</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.7878999999999999</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.65246</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.57213</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.41416</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.49662</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0.43326</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0.42276</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0.43109</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>0.57935</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>0.20889</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>0.83625</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0.27216</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>0.25519</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0.45951</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>0.78977</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CM112" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="CN112" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CO112" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CP112" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="CQ112" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="CR112" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CS112" t="n">
+        <v>0.32214</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>0.18295</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>0.23946</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>0.15273</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>0.1553</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>0.16203</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>-0.01553</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>0.06165</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>0.14409</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>0.14483</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>0.14468</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>0.26896</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>0.14721</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>0.14676</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>0.11528</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>0.11435</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>0.15448</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>0.14566</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>0.15113</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BU113" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="BV113" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BW113" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="BX113" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BY113" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="BZ113" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>0.44566</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="CG113" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>0.44003</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>0.44286</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CM113" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="CN113" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="CO113" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="CP113" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CQ113" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CR113" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CS113" t="n">
+        <v>0.34714</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.5324099999999999</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.46439</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.4205</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="X114" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>0.27091</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>0.26641</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>0.20675</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>0.24443</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>0.26992</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CR114" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CS114" t="n">
+        <v>0.35888</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.51124</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>0.66844</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0.81047</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0.79667</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>0.73268</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0.93375</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>0.61349</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>0.42101</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0.69302</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>0.51707</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>0.23129</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>0.34817</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.46668</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>0.34897</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.65685</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7609900000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34364</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.26798</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.15741</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.20538</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.22239</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.26138</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.28056</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6337999999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.59737</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.59436</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.46601</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.73077</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.47585</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.80123</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.47373</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46632</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42777</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.359</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.82509</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.48615</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5278400000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.51314</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.68726</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44438</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.41413</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.4084100000000001</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.41443</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.44547</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.55225</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49433</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.44614</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.8284</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.44579</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.44984</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.55564</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.40885</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41903</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.67811</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5895199999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.49761</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.50264</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.53704</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.70908</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.71448</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.52647</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.8007300000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.5815</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.52403</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.8285</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.77475</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.62487</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.67462</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.44443</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.48037</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.47366</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.46738</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.54979</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.45144</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.20922</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.01731</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.45798</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.18105</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.36235</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.23133</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.25051</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.13577</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.24544</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04231</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.25004</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.17203</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.18751</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.23318</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.25539</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26288</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23235</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34705</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.26661</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.18084</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0.24101</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0.00069</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.01672</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>0.12767</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03932</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>-0.01445</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.03992</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03707999999999999</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04794</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04747</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.02465</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.02549</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.0266</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04926</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.03989</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.20149</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.25882</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.2799700000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.48185</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.5449700000000001</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.21544</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.8354600000000001</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.83849</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.25281</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28605</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.26634</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.26395</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.24722</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.82547</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.7446799999999999</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.74158</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.83985</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.22542</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.19083</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.16357</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.18281</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.16446</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>-0.03553</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>-0.01664</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.19286</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.19934</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.17081</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.18313</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.17835</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.25671</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>1.0675</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.9146299999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.51349</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.75181</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.9147799999999999</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.91479</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.17506</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>1.34193</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.1186</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.10718</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.32154</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.82208</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.6256499999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.56308</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.49562</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.42672</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1.06321</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.5220399999999999</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5323600000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60222</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.8543200000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.44004</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.14183</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.40345</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.42887</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>1.16841</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.49778</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.44481</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.52667</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35309</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.27699</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.46079</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.6370800000000001</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>1.54382</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.82333</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.17112</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.64075</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.49611</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.26115</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.48517</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.49152</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.80576</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.8759</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.5219400000000001</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.48135</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.36733</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.50136</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.27481</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.52906</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.43013</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.43034</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.51189</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.5845199999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.59688</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.57323</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.77706</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.7893600000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.50361</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.54661</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.68096</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.5955499999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.14175</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74453</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.04431</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.77888</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.8399099999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37174</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.16484</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.07102</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.19464</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.21171</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.05768</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.07274</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.08449</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24319</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.08706999999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.05997</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.19531</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.16271</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.17843</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54301</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.42452</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.51335</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.50273</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.36701</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.9283899999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.5171399999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.45663</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.45797</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.42826</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.4353399999999999</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.63635</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.69948</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.02054</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.68676</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.15434</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.74209</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.53472</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.64767</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.6507200000000001</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.49704</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.77662</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40543</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.58063</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.42996</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3615</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.7509199999999999</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.57286</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.15776</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.26216</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.61214</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.53795</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1.1722</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.45751</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.5063799999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.19442</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.22529</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.13503</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.1376</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.6222799999999999</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.12922</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.2123</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.47721</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.37595</v>
       </c>
     </row>
   </sheetData>
